--- a/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/VADODRA.xlsx
+++ b/06_Office_Related/01_NSO_work/06_SL_to_PIVOT_to_Compare_with_WP/02_GJ_WP_2026-27/SL 2.0/VADODRA.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="24729"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\2026-27\ICS\2.0   PLANNING 2026-27\Kharif 2026-27\2.0\2.0 planning 2026-27\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05 GIT\01_masterRepo\06_Office_Related\01_NSO_work\06_SL_to_PIVOT_to_Compare_with_WP\02_GJ_WP_2026-27\SL 2.0\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{948F5A6A-550E-47A8-BB6C-2EF042DF7E09}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E3576A9B-D251-49FC-8F9D-3823A6B0773B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-109" yWindow="-109" windowWidth="26301" windowHeight="14169" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="central 2.0" sheetId="1" r:id="rId1"/>
@@ -531,10 +531,26 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="4" borderId="11" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -555,22 +571,6 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="12" xfId="1" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -853,115 +853,115 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:L32"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.5703125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="15.42578125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="16.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="15.375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="16.25" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+    </row>
+    <row r="2" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-    </row>
-    <row r="3" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="3" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="18">
         <v>10</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18">
         <v>14</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18">
         <v>12</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22">
+      <c r="I4" s="18"/>
+      <c r="J4" s="18">
         <v>14</v>
       </c>
-      <c r="K4" s="22"/>
+      <c r="K4" s="18"/>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="26" t="s">
+    <row r="5" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26" t="s">
+      <c r="I5" s="20"/>
+      <c r="J5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="20"/>
       <c r="L5" s="2">
         <f>SUM(D4:K4)</f>
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="32.6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -997,7 +997,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1025,7 +1025,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1049,7 +1049,7 @@
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1073,7 +1073,7 @@
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -1093,7 +1093,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -1117,7 +1117,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -1137,7 +1137,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -1165,7 +1165,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A14" s="6" t="s">
         <v>29</v>
       </c>
@@ -1192,7 +1192,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A15" s="6" t="s">
         <v>29</v>
       </c>
@@ -1219,7 +1219,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A16" s="6" t="s">
         <v>32</v>
       </c>
@@ -1250,7 +1250,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A17" s="6" t="s">
         <v>34</v>
       </c>
@@ -1285,7 +1285,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A18" s="6" t="s">
         <v>34</v>
       </c>
@@ -1316,7 +1316,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A19" s="6" t="s">
         <v>37</v>
       </c>
@@ -1351,7 +1351,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A20" s="6" t="s">
         <v>39</v>
       </c>
@@ -1382,7 +1382,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
       <c r="A21" s="6" t="s">
         <v>41</v>
       </c>
@@ -1417,12 +1417,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="22" t="s">
+    <row r="22" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A22" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B22" s="22"/>
-      <c r="C22" s="22"/>
+      <c r="B22" s="18"/>
+      <c r="C22" s="18"/>
       <c r="D22" s="1">
         <f>SUM(D14:D21)</f>
         <v>2</v>
@@ -1448,27 +1448,27 @@
         <v>34</v>
       </c>
     </row>
-    <row r="23" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A23" s="15" t="s">
+    <row r="23" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A23" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B23" s="15"/>
-      <c r="C23" s="15"/>
-      <c r="D23" s="15"/>
-      <c r="E23" s="15"/>
-      <c r="F23" s="15"/>
-      <c r="G23" s="15"/>
-      <c r="H23" s="15"/>
-      <c r="I23" s="15"/>
-      <c r="J23" s="15"/>
-      <c r="K23" s="15"/>
-      <c r="L23" s="15"/>
-    </row>
-    <row r="24" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B23" s="19"/>
+      <c r="C23" s="19"/>
+      <c r="D23" s="19"/>
+      <c r="E23" s="19"/>
+      <c r="F23" s="19"/>
+      <c r="G23" s="19"/>
+      <c r="H23" s="19"/>
+      <c r="I23" s="19"/>
+      <c r="J23" s="19"/>
+      <c r="K23" s="19"/>
+      <c r="L23" s="19"/>
+    </row>
+    <row r="24" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>71</v>
       </c>
-      <c r="B24" s="27" t="s">
+      <c r="B24" s="14" t="s">
         <v>73</v>
       </c>
       <c r="C24" s="7" t="s">
@@ -1491,11 +1491,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A25" s="4" t="s">
         <v>74</v>
       </c>
-      <c r="B25" s="27" t="s">
+      <c r="B25" s="14" t="s">
         <v>69</v>
       </c>
       <c r="C25" s="7" t="s">
@@ -1518,11 +1518,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A26" s="4" t="s">
         <v>34</v>
       </c>
-      <c r="B26" s="27" t="s">
+      <c r="B26" s="14" t="s">
         <v>69</v>
       </c>
       <c r="C26" s="7" t="s">
@@ -1545,7 +1545,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="27" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A27" s="4" t="s">
         <v>34</v>
       </c>
@@ -1572,11 +1572,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="28" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A28" s="4" t="s">
         <v>37</v>
       </c>
-      <c r="B28" s="27" t="s">
+      <c r="B28" s="14" t="s">
         <v>73</v>
       </c>
       <c r="C28" s="7" t="s">
@@ -1599,11 +1599,11 @@
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A29" s="4" t="s">
         <v>39</v>
       </c>
-      <c r="B29" s="27" t="s">
+      <c r="B29" s="14" t="s">
         <v>70</v>
       </c>
       <c r="C29" s="7" t="s">
@@ -1626,7 +1626,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
         <v>41</v>
       </c>
@@ -1657,12 +1657,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="31" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A31" s="23" t="s">
+    <row r="31" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A31" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B31" s="24"/>
-      <c r="C31" s="25"/>
+      <c r="B31" s="16"/>
+      <c r="C31" s="17"/>
       <c r="D31" s="1">
         <f>SUM(D24:D30)</f>
         <v>8</v>
@@ -1688,12 +1688,12 @@
         <v>16</v>
       </c>
     </row>
-    <row r="32" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A32" s="23" t="s">
+    <row r="32" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A32" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B32" s="24"/>
-      <c r="C32" s="25"/>
+      <c r="B32" s="16"/>
+      <c r="C32" s="17"/>
       <c r="D32" s="1">
         <f>+D22+D31</f>
         <v>10</v>
@@ -1721,14 +1721,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A32:C32"/>
-    <mergeCell ref="A22:C22"/>
-    <mergeCell ref="A23:L23"/>
-    <mergeCell ref="A31:C31"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -1738,6 +1730,14 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A32:C32"/>
+    <mergeCell ref="A22:C22"/>
+    <mergeCell ref="A23:L23"/>
+    <mergeCell ref="A31:C31"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
@@ -1746,114 +1746,114 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:L26"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.3" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="12.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="13.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="12.25" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="13.75" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="14" t="s">
+    <row r="1" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A1" s="21" t="s">
         <v>27</v>
       </c>
-      <c r="B1" s="14"/>
-      <c r="C1" s="14"/>
-      <c r="D1" s="14"/>
-      <c r="E1" s="14"/>
-      <c r="F1" s="14"/>
-      <c r="G1" s="14"/>
-      <c r="H1" s="14"/>
-      <c r="I1" s="14"/>
-      <c r="J1" s="14"/>
-      <c r="K1" s="14"/>
-      <c r="L1" s="14"/>
-    </row>
-    <row r="2" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="14" t="s">
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
+      <c r="F1" s="21"/>
+      <c r="G1" s="21"/>
+      <c r="H1" s="21"/>
+      <c r="I1" s="21"/>
+      <c r="J1" s="21"/>
+      <c r="K1" s="21"/>
+      <c r="L1" s="21"/>
+    </row>
+    <row r="2" spans="1:12" ht="19.05" x14ac:dyDescent="0.25">
+      <c r="A2" s="21" t="s">
         <v>1</v>
       </c>
-      <c r="B2" s="14"/>
-      <c r="C2" s="14"/>
-      <c r="D2" s="14"/>
-      <c r="E2" s="14"/>
-      <c r="F2" s="14"/>
-      <c r="G2" s="14"/>
-      <c r="H2" s="14"/>
-      <c r="I2" s="14"/>
-      <c r="J2" s="14"/>
-      <c r="K2" s="14"/>
-      <c r="L2" s="14"/>
-    </row>
-    <row r="3" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="15" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3" s="15"/>
-      <c r="C3" s="15"/>
-      <c r="D3" s="15"/>
-      <c r="E3" s="15"/>
-      <c r="F3" s="15"/>
-      <c r="G3" s="15"/>
-      <c r="H3" s="15"/>
-      <c r="I3" s="15"/>
-      <c r="J3" s="15"/>
-      <c r="K3" s="15"/>
-      <c r="L3" s="15"/>
-    </row>
-    <row r="4" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="16" t="s">
+      <c r="B2" s="21"/>
+      <c r="C2" s="21"/>
+      <c r="D2" s="21"/>
+      <c r="E2" s="21"/>
+      <c r="F2" s="21"/>
+      <c r="G2" s="21"/>
+      <c r="H2" s="21"/>
+      <c r="I2" s="21"/>
+      <c r="J2" s="21"/>
+      <c r="K2" s="21"/>
+      <c r="L2" s="21"/>
+    </row>
+    <row r="3" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A3" s="19" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3" s="19"/>
+      <c r="C3" s="19"/>
+      <c r="D3" s="19"/>
+      <c r="E3" s="19"/>
+      <c r="F3" s="19"/>
+      <c r="G3" s="19"/>
+      <c r="H3" s="19"/>
+      <c r="I3" s="19"/>
+      <c r="J3" s="19"/>
+      <c r="K3" s="19"/>
+      <c r="L3" s="19"/>
+    </row>
+    <row r="4" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A4" s="22" t="s">
         <v>43</v>
       </c>
-      <c r="B4" s="17"/>
-      <c r="C4" s="20" t="s">
+      <c r="B4" s="23"/>
+      <c r="C4" s="26" t="s">
         <v>28</v>
       </c>
-      <c r="D4" s="22">
+      <c r="D4" s="18">
         <v>4</v>
       </c>
-      <c r="E4" s="22"/>
-      <c r="F4" s="22">
+      <c r="E4" s="18"/>
+      <c r="F4" s="18">
         <v>8</v>
       </c>
-      <c r="G4" s="22"/>
-      <c r="H4" s="22">
+      <c r="G4" s="18"/>
+      <c r="H4" s="18">
         <v>8</v>
       </c>
-      <c r="I4" s="22"/>
-      <c r="J4" s="22">
+      <c r="I4" s="18"/>
+      <c r="J4" s="18">
         <v>8</v>
       </c>
-      <c r="K4" s="22"/>
+      <c r="K4" s="18"/>
       <c r="L4" s="2" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="18"/>
-      <c r="B5" s="19"/>
-      <c r="C5" s="21"/>
-      <c r="D5" s="26" t="s">
+    <row r="5" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A5" s="24"/>
+      <c r="B5" s="25"/>
+      <c r="C5" s="27"/>
+      <c r="D5" s="20" t="s">
         <v>4</v>
       </c>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26" t="s">
+      <c r="E5" s="20"/>
+      <c r="F5" s="20" t="s">
         <v>5</v>
       </c>
-      <c r="G5" s="26"/>
-      <c r="H5" s="26" t="s">
+      <c r="G5" s="20"/>
+      <c r="H5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="I5" s="26"/>
-      <c r="J5" s="26" t="s">
+      <c r="I5" s="20"/>
+      <c r="J5" s="20" t="s">
         <v>7</v>
       </c>
-      <c r="K5" s="26"/>
+      <c r="K5" s="20"/>
       <c r="L5" s="2">
         <f>SUM(D4:K4)</f>
         <v>28</v>
       </c>
     </row>
-    <row r="6" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:12" ht="32.6" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>8</v>
       </c>
@@ -1889,7 +1889,7 @@
       </c>
       <c r="L6" s="4"/>
     </row>
-    <row r="7" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>13</v>
       </c>
@@ -1917,7 +1917,7 @@
       <c r="K7" s="4"/>
       <c r="L7" s="4"/>
     </row>
-    <row r="8" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>15</v>
       </c>
@@ -1941,7 +1941,7 @@
       </c>
       <c r="L8" s="4"/>
     </row>
-    <row r="9" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>15</v>
       </c>
@@ -1965,7 +1965,7 @@
       </c>
       <c r="L9" s="4"/>
     </row>
-    <row r="10" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>17</v>
       </c>
@@ -1985,7 +1985,7 @@
       <c r="K10" s="4"/>
       <c r="L10" s="4"/>
     </row>
-    <row r="11" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>17</v>
       </c>
@@ -2009,7 +2009,7 @@
       <c r="K11" s="4"/>
       <c r="L11" s="4"/>
     </row>
-    <row r="12" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>20</v>
       </c>
@@ -2029,7 +2029,7 @@
       <c r="K12" s="4"/>
       <c r="L12" s="4"/>
     </row>
-    <row r="13" spans="1:12" ht="28.5" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>20</v>
       </c>
@@ -2057,7 +2057,7 @@
       <c r="K13" s="4"/>
       <c r="L13" s="4"/>
     </row>
-    <row r="14" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" ht="19.05" x14ac:dyDescent="0.35">
       <c r="A14" s="8" t="s">
         <v>29</v>
       </c>
@@ -2088,7 +2088,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="15" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" ht="19.05" x14ac:dyDescent="0.35">
       <c r="A15" s="8" t="s">
         <v>29</v>
       </c>
@@ -2111,7 +2111,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" ht="19.05" x14ac:dyDescent="0.35">
       <c r="A16" s="8" t="s">
         <v>32</v>
       </c>
@@ -2142,7 +2142,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="17" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:12" ht="19.05" x14ac:dyDescent="0.35">
       <c r="A17" s="8" t="s">
         <v>32</v>
       </c>
@@ -2169,7 +2169,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:12" ht="19.05" x14ac:dyDescent="0.35">
       <c r="A18" s="8" t="s">
         <v>32</v>
       </c>
@@ -2200,7 +2200,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="19" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:12" ht="19.05" x14ac:dyDescent="0.35">
       <c r="A19" s="8" t="s">
         <v>37</v>
       </c>
@@ -2231,7 +2231,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="20" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:12" ht="19.05" x14ac:dyDescent="0.35">
       <c r="A20" s="8" t="s">
         <v>41</v>
       </c>
@@ -2266,12 +2266,12 @@
         <v>6</v>
       </c>
     </row>
-    <row r="21" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A21" s="22" t="s">
+    <row r="21" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A21" s="18" t="s">
         <v>23</v>
       </c>
-      <c r="B21" s="22"/>
-      <c r="C21" s="22"/>
+      <c r="B21" s="18"/>
+      <c r="C21" s="18"/>
       <c r="D21" s="1">
         <f>SUM(D14:D20)</f>
         <v>4</v>
@@ -2297,23 +2297,23 @@
         <v>24</v>
       </c>
     </row>
-    <row r="22" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A22" s="15" t="s">
+    <row r="22" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A22" s="19" t="s">
         <v>24</v>
       </c>
-      <c r="B22" s="15"/>
-      <c r="C22" s="15"/>
-      <c r="D22" s="15"/>
-      <c r="E22" s="15"/>
-      <c r="F22" s="15"/>
-      <c r="G22" s="15"/>
-      <c r="H22" s="15"/>
-      <c r="I22" s="15"/>
-      <c r="J22" s="15"/>
-      <c r="K22" s="15"/>
-      <c r="L22" s="15"/>
-    </row>
-    <row r="23" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B22" s="19"/>
+      <c r="C22" s="19"/>
+      <c r="D22" s="19"/>
+      <c r="E22" s="19"/>
+      <c r="F22" s="19"/>
+      <c r="G22" s="19"/>
+      <c r="H22" s="19"/>
+      <c r="I22" s="19"/>
+      <c r="J22" s="19"/>
+      <c r="K22" s="19"/>
+      <c r="L22" s="19"/>
+    </row>
+    <row r="23" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A23" s="4" t="s">
         <v>44</v>
       </c>
@@ -2340,7 +2340,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="24" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
       <c r="A24" s="4" t="s">
         <v>59</v>
       </c>
@@ -2367,12 +2367,12 @@
         <v>2</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A25" s="23" t="s">
+    <row r="25" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A25" s="15" t="s">
         <v>25</v>
       </c>
-      <c r="B25" s="24"/>
-      <c r="C25" s="25"/>
+      <c r="B25" s="16"/>
+      <c r="C25" s="17"/>
       <c r="D25" s="1">
         <f>SUM(D23:D24)</f>
         <v>0</v>
@@ -2398,12 +2398,12 @@
         <v>4</v>
       </c>
     </row>
-    <row r="26" spans="1:12" ht="28.5" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A26" s="23" t="s">
+    <row r="26" spans="1:12" ht="16.3" x14ac:dyDescent="0.25">
+      <c r="A26" s="15" t="s">
         <v>26</v>
       </c>
-      <c r="B26" s="24"/>
-      <c r="C26" s="25"/>
+      <c r="B26" s="16"/>
+      <c r="C26" s="17"/>
       <c r="D26" s="1">
         <f>+D21+D25</f>
         <v>4</v>
@@ -2431,14 +2431,6 @@
     </row>
   </sheetData>
   <mergeCells count="17">
-    <mergeCell ref="A22:L22"/>
-    <mergeCell ref="A25:C25"/>
-    <mergeCell ref="A26:C26"/>
-    <mergeCell ref="D5:E5"/>
-    <mergeCell ref="F5:G5"/>
-    <mergeCell ref="H5:I5"/>
-    <mergeCell ref="J5:K5"/>
-    <mergeCell ref="A21:C21"/>
     <mergeCell ref="A1:L1"/>
     <mergeCell ref="A2:L2"/>
     <mergeCell ref="A3:L3"/>
@@ -2448,6 +2440,14 @@
     <mergeCell ref="F4:G4"/>
     <mergeCell ref="H4:I4"/>
     <mergeCell ref="J4:K4"/>
+    <mergeCell ref="A22:L22"/>
+    <mergeCell ref="A25:C25"/>
+    <mergeCell ref="A26:C26"/>
+    <mergeCell ref="D5:E5"/>
+    <mergeCell ref="F5:G5"/>
+    <mergeCell ref="H5:I5"/>
+    <mergeCell ref="J5:K5"/>
+    <mergeCell ref="A21:C21"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
